--- a/Documents/DS&AS Budget.xlsx
+++ b/Documents/DS&AS Budget.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DSAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DSAS\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1782,14 +1782,14 @@
         <v>43</v>
       </c>
       <c r="C30" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <v>200000</v>
       </c>
       <c r="E30" s="5">
         <f t="shared" si="0"/>
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>14</v>
@@ -1872,14 +1872,14 @@
         <v>44</v>
       </c>
       <c r="C33" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" s="5">
         <v>40000</v>
       </c>
       <c r="E33" s="5">
         <f t="shared" si="0"/>
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>14</v>
@@ -2685,14 +2685,14 @@
         <v>71</v>
       </c>
       <c r="C61" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" s="5">
         <v>25000</v>
       </c>
       <c r="E61" s="5">
         <f t="shared" si="0"/>
-        <v>25000</v>
+        <v>75000</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>14</v>
@@ -2793,14 +2793,14 @@
         <v>74</v>
       </c>
       <c r="C64" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" s="5">
         <v>30000</v>
       </c>
       <c r="E64" s="5">
         <f t="shared" si="0"/>
-        <v>30000</v>
+        <v>90000</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>14</v>
@@ -3780,7 +3780,7 @@
       <c r="D100" s="8"/>
       <c r="E100" s="8">
         <f>SUM(E3:E99)</f>
-        <v>9024680</v>
+        <v>9414680</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
